--- a/Rowing.xlsx
+++ b/Rowing.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luis\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Flutter\rowing_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFA521F8-39D7-4B97-B756-CC22A560CA85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F848B5-55C9-4145-ADB6-D709E768FFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{98999F70-D1D4-4A66-BAFC-041518B5B1BB}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="521">
   <si>
     <t>Rowing</t>
   </si>
@@ -1103,12 +1103,6 @@
     <t>CHANTAL</t>
   </si>
   <si>
-    <t>ELLA123</t>
-  </si>
-  <si>
-    <t>DAIANA</t>
-  </si>
-  <si>
     <t>HablitaApp</t>
   </si>
   <si>
@@ -1263,9 +1257,6 @@
   </si>
   <si>
     <t>190.136.50.247</t>
-  </si>
-  <si>
-    <t>SELECT IdUsuario,Login, Contrasena, Nombre, Apellido, HabilitaAPP, HabilitaFotos,HabilitaSSHH,HabilitaMedidores, HabilitaReclamos, Modulo FROM Usuarios WHERE HabilitaAPP=1</t>
   </si>
   <si>
     <t>IdUsuario</t>
@@ -1667,6 +1658,18 @@
   </si>
   <si>
     <t>ORDER BY NROREGISTRO DESC</t>
+  </si>
+  <si>
+    <t>Gonzalo</t>
+  </si>
+  <si>
+    <t>FROM     Usuarios</t>
+  </si>
+  <si>
+    <t>WHERE  (HabilitaAPP = 1)</t>
+  </si>
+  <si>
+    <t>SELECT IdUsuario, CODIGOGRUPO,CODIGOCAUSANTE,Login, Contrasena, Nombre, Apellido, HabilitaAPP, HabilitaFotos, HabilitaSSHH, HabilitaRRHH,HabilitaMedidores, HabilitaReclamos, HabilitaFlotas, Modulo</t>
   </si>
 </sst>
 </file>
@@ -2270,7 +2273,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5AE46312-847B-40D1-8980-D7DCC506F668}">
-  <dimension ref="A1:DW101"/>
+  <dimension ref="A1:DW103"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.44140625" style="1" bestFit="1" customWidth="1"/>
@@ -2293,30 +2296,30 @@
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E1" s="1">
         <v>382737678</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="N2" s="1">
         <v>0</v>
@@ -2325,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="P2" s="21" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
@@ -2336,10 +2339,10 @@
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="N3" s="1">
         <v>1</v>
@@ -2359,7 +2362,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="N4" s="1">
         <v>2</v>
@@ -2379,7 +2382,7 @@
         <v>16</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="N5" s="1">
         <v>3</v>
@@ -2388,7 +2391,7 @@
         <v>10</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
@@ -2408,7 +2411,7 @@
         <v>3</v>
       </c>
       <c r="P6" s="21" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
@@ -2427,6 +2430,9 @@
       <c r="A8" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="I8" s="4" t="s">
         <v>324</v>
       </c>
@@ -2436,12 +2442,15 @@
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
       <c r="P8" s="3" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>325</v>
@@ -2454,15 +2463,12 @@
         <v>329</v>
       </c>
       <c r="P9" s="24" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N10" s="23"/>
       <c r="P10" s="8" t="s">
@@ -2471,341 +2477,264 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B11" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B12" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="1">
-        <v>1</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>343</v>
+      <c r="C12" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="N14" s="1" t="s">
-        <v>344</v>
-      </c>
+      <c r="B14" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B15" s="8" t="s">
-        <v>393</v>
-      </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="J15" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B16" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="J17" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="N15" s="1" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="K16" s="3" t="s">
+      <c r="N17" s="1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="K18" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="17" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B17" s="5" t="s">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B19" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="K19" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="18" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B18" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="Q18" s="25" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="B19" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>513</v>
+      <c r="Q19" s="3" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="20" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B20" s="4" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>514</v>
+        <v>333</v>
+      </c>
+      <c r="Q20" s="25" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="21" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B21" s="4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="22" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" s="6">
-        <v>456789</v>
+        <v>29</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>213</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>381</v>
+        <v>511</v>
       </c>
     </row>
     <row r="23" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B23" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>43</v>
+        <v>36</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>340</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>382</v>
+        <v>512</v>
       </c>
     </row>
     <row r="24" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B24" s="4" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C24" s="6">
-        <v>15032021</v>
+        <v>456789</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I24" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L24" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="M24" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="N24" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="O24" s="5" t="s">
-        <v>334</v>
+        <v>39</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="25" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="G25" s="16">
-        <v>172</v>
-      </c>
-      <c r="H25" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="I25" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="J25" s="17" t="s">
-        <v>336</v>
-      </c>
-      <c r="K25" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="L25" s="17">
-        <v>1</v>
-      </c>
-      <c r="M25" s="17">
-        <v>1</v>
-      </c>
-      <c r="N25" s="17">
-        <v>0</v>
-      </c>
-      <c r="O25" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="25" t="s">
-        <v>517</v>
+        <v>43</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="26" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B26" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>52</v>
+        <v>44</v>
+      </c>
+      <c r="C26" s="6">
+        <v>15032021</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26" s="16">
-        <v>292</v>
-      </c>
-      <c r="H26" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="I26" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="J26" s="17" t="s">
-        <v>337</v>
-      </c>
-      <c r="K26" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="L26" s="17">
-        <v>1</v>
-      </c>
-      <c r="M26" s="17">
-        <v>0</v>
-      </c>
-      <c r="N26" s="17">
-        <v>0</v>
-      </c>
-      <c r="O26" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>509</v>
+        <v>46</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="N26" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="27" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B27" s="4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="G27" s="16">
-        <v>173</v>
+        <v>50</v>
+      </c>
+      <c r="F27" s="16">
+        <v>172</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>21</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>26</v>
+        <v>336</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>338</v>
-      </c>
-      <c r="K27" s="17" t="s">
-        <v>28</v>
+        <v>24</v>
+      </c>
+      <c r="K27" s="17">
+        <v>1</v>
       </c>
       <c r="L27" s="17">
         <v>1</v>
@@ -2817,45 +2746,48 @@
         <v>0</v>
       </c>
       <c r="O27" s="17">
-        <v>1</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>311</v>
+        <v>0</v>
+      </c>
+      <c r="Q27" s="25" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="28" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B28" s="4" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28" s="16">
-        <v>174</v>
+        <v>54</v>
+      </c>
+      <c r="F28" s="16">
+        <v>292</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>67</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="I28" s="17" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>340</v>
-      </c>
-      <c r="K28" s="17" t="s">
-        <v>32</v>
+        <v>70</v>
+      </c>
+      <c r="K28" s="17">
+        <v>1</v>
       </c>
       <c r="L28" s="17">
         <v>0</v>
       </c>
-      <c r="M28" s="17" t="s">
-        <v>117</v>
+      <c r="M28" s="17">
+        <v>0</v>
       </c>
       <c r="N28" s="17">
         <v>0</v>
@@ -2864,384 +2796,414 @@
         <v>0</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
     </row>
     <row r="29" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B29" s="4" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>66</v>
+        <v>58</v>
+      </c>
+      <c r="F29" s="16">
+        <v>173</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H29" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I29" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="K29" s="17">
+        <v>1</v>
+      </c>
+      <c r="L29" s="17">
+        <v>0</v>
+      </c>
+      <c r="M29" s="17">
+        <v>1</v>
+      </c>
+      <c r="N29" s="17">
+        <v>0</v>
+      </c>
+      <c r="O29" s="17">
+        <v>0</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>519</v>
+        <v>311</v>
       </c>
     </row>
     <row r="30" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B30" s="4" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="F30" s="16">
+        <v>203</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="H30" s="17" t="s">
+        <v>425</v>
+      </c>
+      <c r="I30" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="J30" s="17" t="s">
+        <v>427</v>
+      </c>
+      <c r="K30" s="17">
+        <v>1</v>
+      </c>
+      <c r="L30" s="17">
+        <v>1</v>
+      </c>
+      <c r="M30" s="17">
+        <v>1</v>
+      </c>
+      <c r="N30" s="17">
+        <v>1</v>
+      </c>
+      <c r="O30" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="31" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B31" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>73</v>
+        <v>66</v>
+      </c>
+      <c r="F31" s="1">
+        <v>2</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>397</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>398</v>
+      </c>
+      <c r="I31" s="17" t="s">
+        <v>517</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="K31" s="17">
+        <v>1</v>
+      </c>
+      <c r="L31" s="17">
+        <v>1</v>
+      </c>
+      <c r="M31" s="17">
+        <v>1</v>
+      </c>
+      <c r="N31" s="17">
+        <v>1</v>
+      </c>
+      <c r="O31" s="17">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="32" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B32" s="4" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B33" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B34" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="B35" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C35" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E35" s="4" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="C36" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="C37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q37" s="23"/>
     </row>
     <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q39" s="23"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="C40" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="C41" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="C43" s="1" t="s">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="C45" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="C44" s="1" t="s">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="C46" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="G47" s="1" t="s">
+    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="G49" s="1" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
-      <c r="E48" s="1">
-        <v>40856</v>
-      </c>
-      <c r="G48" s="1">
-        <v>3</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="E49" s="1">
-        <v>40932</v>
-      </c>
-      <c r="G49" s="1">
-        <v>2</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.2">
       <c r="E50" s="1">
+        <v>40856</v>
+      </c>
+      <c r="G50" s="1">
+        <v>3</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="E51" s="1">
+        <v>40932</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="E52" s="1">
         <v>43079</v>
       </c>
-      <c r="G50" s="1">
-        <v>1</v>
-      </c>
-      <c r="H50" s="1" t="s">
+      <c r="G52" s="1">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A56" s="1" t="s">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B58" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C56" s="8" t="s">
+      <c r="C58" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="D58" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E58" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F56" s="8" t="s">
+      <c r="F58" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G58" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H58" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="I58" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="J56" s="8" t="s">
+      <c r="J58" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="K56" s="8" t="s">
+      <c r="K58" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="L56" s="8" t="s">
+      <c r="L58" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="M56" s="8" t="s">
+      <c r="M58" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="N56" s="8" t="s">
+      <c r="N58" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="O56" s="8" t="s">
+      <c r="O58" s="8" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A57" s="1">
-        <v>1</v>
-      </c>
-      <c r="B57" s="8">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>1</v>
+      </c>
+      <c r="B59" s="8">
         <v>521</v>
       </c>
-      <c r="C57" s="8" t="s">
+      <c r="C59" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="D57" s="8"/>
-      <c r="E57" s="7">
+      <c r="D59" s="8"/>
+      <c r="E59" s="7">
         <v>43514</v>
       </c>
-      <c r="F57" s="8" t="s">
+      <c r="F59" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="G57" s="1">
+      <c r="G59" s="1">
         <v>180</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H59" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="J57" s="8" t="s">
+      <c r="J59" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="K57" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="L57" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="M57" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="N57" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="O57" s="8" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="65" spans="1:127" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
+      <c r="K59" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="N59" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="O59" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="67" spans="1:127" x14ac:dyDescent="0.2">
+      <c r="A67" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C67" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E67" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F67" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="G67" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="H67" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I65" s="1" t="s">
+      <c r="I67" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="J65" s="1" t="s">
+      <c r="J67" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="K65" s="1" t="s">
+      <c r="K67" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="L65" s="1" t="s">
+      <c r="L67" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="M65" s="1" t="s">
+      <c r="M67" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="N65" s="1" t="s">
+      <c r="N67" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="O65" s="1" t="s">
+      <c r="O67" s="1" t="s">
         <v>112</v>
-      </c>
-    </row>
-    <row r="66" spans="1:127" x14ac:dyDescent="0.2">
-      <c r="A66" s="1">
-        <v>1333</v>
-      </c>
-      <c r="B66" s="1">
-        <v>40856</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E66" s="7">
-        <v>44440</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="H66" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="I66" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="J66" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="M66" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="67" spans="1:127" x14ac:dyDescent="0.2">
-      <c r="A67" s="1">
-        <v>1334</v>
-      </c>
-      <c r="B67" s="1">
-        <v>40856</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="E67" s="7">
-        <v>44442</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="M67" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="N67" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="68" spans="1:127" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="B68" s="1">
         <v>40856</v>
@@ -3250,21 +3212,21 @@
         <v>117</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E68" s="7">
-        <v>44460</v>
+        <v>44440</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="G68" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="H68" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="I68" s="1" t="s">
+      <c r="I68" s="8" t="s">
         <v>121</v>
       </c>
       <c r="J68" s="1" t="s">
@@ -3279,902 +3241,926 @@
       <c r="M68" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="N68" s="1">
-        <v>0</v>
+      <c r="N68" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="O68" s="1" t="s">
         <v>117</v>
       </c>
     </row>
+    <row r="69" spans="1:127" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>1334</v>
+      </c>
+      <c r="B69" s="1">
+        <v>40856</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E69" s="7">
+        <v>44442</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L69" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
     <row r="70" spans="1:127" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>1335</v>
+      </c>
+      <c r="B70" s="1">
+        <v>40856</v>
+      </c>
       <c r="C70" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E70" s="7">
+        <v>44460</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L70" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="N70" s="1">
+        <v>0</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="72" spans="1:127" x14ac:dyDescent="0.2">
+      <c r="C72" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F72" s="1" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="74" spans="1:127" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
+    <row r="76" spans="1:127" x14ac:dyDescent="0.2">
+      <c r="A76" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C76" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D76" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E76" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F76" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="G76" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="H76" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="I74" s="1" t="s">
+      <c r="I76" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="J74" s="1" t="s">
+      <c r="J76" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="K74" s="1" t="s">
+      <c r="K76" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="L74" s="1" t="s">
+      <c r="L76" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="M74" s="1" t="s">
+      <c r="M76" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="N74" s="1" t="s">
+      <c r="N76" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="O74" s="1" t="s">
+      <c r="O76" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="P74" s="1" t="s">
+      <c r="P76" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="Q74" s="1" t="s">
+      <c r="Q76" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="R74" s="1" t="s">
+      <c r="R76" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="S74" s="1" t="s">
+      <c r="S76" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="T74" s="1" t="s">
+      <c r="T76" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="U74" s="1" t="s">
+      <c r="U76" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="V74" s="1" t="s">
+      <c r="V76" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="W74" s="1" t="s">
+      <c r="W76" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="X74" s="1" t="s">
+      <c r="X76" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="Y74" s="1" t="s">
+      <c r="Y76" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="Z74" s="1" t="s">
+      <c r="Z76" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="AA74" s="8" t="s">
+      <c r="AA76" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="AB74" s="1" t="s">
+      <c r="AB76" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="AC74" s="1" t="s">
+      <c r="AC76" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="AD74" s="1" t="s">
+      <c r="AD76" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="AE74" s="1" t="s">
+      <c r="AE76" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="AF74" s="1" t="s">
+      <c r="AF76" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="AG74" s="1" t="s">
+      <c r="AG76" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="AH74" s="1" t="s">
+      <c r="AH76" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="AI74" s="1" t="s">
+      <c r="AI76" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="AJ74" s="1" t="s">
+      <c r="AJ76" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="AK74" s="1" t="s">
+      <c r="AK76" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="AL74" s="1" t="s">
+      <c r="AL76" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="AM74" s="1" t="s">
+      <c r="AM76" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="AN74" s="1" t="s">
+      <c r="AN76" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="AO74" s="1" t="s">
+      <c r="AO76" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="AP74" s="1" t="s">
+      <c r="AP76" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="AQ74" s="1" t="s">
+      <c r="AQ76" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="AR74" s="1" t="s">
+      <c r="AR76" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="AS74" s="1" t="s">
+      <c r="AS76" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="AT74" s="1" t="s">
+      <c r="AT76" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="AU74" s="1" t="s">
+      <c r="AU76" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="AV74" s="1" t="s">
+      <c r="AV76" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="AW74" s="1" t="s">
+      <c r="AW76" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="AX74" s="1" t="s">
+      <c r="AX76" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="AY74" s="1" t="s">
+      <c r="AY76" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="AZ74" s="1" t="s">
+      <c r="AZ76" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="BA74" s="1" t="s">
+      <c r="BA76" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="BB74" s="1" t="s">
+      <c r="BB76" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="BC74" s="1" t="s">
+      <c r="BC76" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="BD74" s="1" t="s">
+      <c r="BD76" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="BE74" s="1" t="s">
+      <c r="BE76" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="BF74" s="1" t="s">
+      <c r="BF76" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="BG74" s="1" t="s">
+      <c r="BG76" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="BH74" s="1" t="s">
+      <c r="BH76" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="BI74" s="1" t="s">
+      <c r="BI76" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="BJ74" s="1" t="s">
+      <c r="BJ76" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="BK74" s="1" t="s">
+      <c r="BK76" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="BL74" s="1" t="s">
+      <c r="BL76" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="BM74" s="1" t="s">
+      <c r="BM76" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="BN74" s="1" t="s">
+      <c r="BN76" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="BO74" s="1" t="s">
+      <c r="BO76" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="BP74" s="1" t="s">
+      <c r="BP76" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="BQ74" s="1" t="s">
+      <c r="BQ76" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="BR74" s="1" t="s">
+      <c r="BR76" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="BS74" s="1" t="s">
+      <c r="BS76" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="BT74" s="1" t="s">
+      <c r="BT76" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="BU74" s="1" t="s">
+      <c r="BU76" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="BV74" s="1" t="s">
+      <c r="BV76" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="BW74" s="1" t="s">
+      <c r="BW76" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="BX74" s="1" t="s">
+      <c r="BX76" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="BY74" s="1" t="s">
+      <c r="BY76" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="BZ74" s="1" t="s">
+      <c r="BZ76" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="CA74" s="1" t="s">
+      <c r="CA76" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="CB74" s="1" t="s">
+      <c r="CB76" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="CC74" s="1" t="s">
+      <c r="CC76" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="CD74" s="1" t="s">
+      <c r="CD76" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="CE74" s="1" t="s">
+      <c r="CE76" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="CF74" s="1" t="s">
+      <c r="CF76" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="CG74" s="1" t="s">
+      <c r="CG76" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="CH74" s="1" t="s">
+      <c r="CH76" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="CI74" s="1" t="s">
+      <c r="CI76" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="CJ74" s="1" t="s">
+      <c r="CJ76" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="CK74" s="8" t="s">
+      <c r="CK76" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="CL74" s="1" t="s">
+      <c r="CL76" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="CM74" s="1" t="s">
+      <c r="CM76" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="CN74" s="1" t="s">
+      <c r="CN76" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="CO74" s="1" t="s">
+      <c r="CO76" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="CP74" s="1" t="s">
+      <c r="CP76" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="CQ74" s="1" t="s">
+      <c r="CQ76" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="CR74" s="1" t="s">
+      <c r="CR76" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="CS74" s="1" t="s">
+      <c r="CS76" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="CT74" s="1" t="s">
+      <c r="CT76" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="CU74" s="1" t="s">
+      <c r="CU76" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="CV74" s="1" t="s">
+      <c r="CV76" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="CW74" s="1" t="s">
+      <c r="CW76" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="CX74" s="1" t="s">
+      <c r="CX76" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="CY74" s="1" t="s">
+      <c r="CY76" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="CZ74" s="1" t="s">
+      <c r="CZ76" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="DA74" s="1" t="s">
+      <c r="DA76" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="DB74" s="1" t="s">
+      <c r="DB76" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="DC74" s="1" t="s">
+      <c r="DC76" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="DD74" s="1" t="s">
+      <c r="DD76" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="DE74" s="1" t="s">
+      <c r="DE76" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="DF74" s="1" t="s">
+      <c r="DF76" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="DG74" s="1" t="s">
+      <c r="DG76" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="DH74" s="1" t="s">
+      <c r="DH76" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="DI74" s="1" t="s">
+      <c r="DI76" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="DJ74" s="1" t="s">
+      <c r="DJ76" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="DK74" s="1" t="s">
+      <c r="DK76" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="DL74" s="1" t="s">
+      <c r="DL76" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="DM74" s="1" t="s">
+      <c r="DM76" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="DN74" s="1" t="s">
+      <c r="DN76" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="DO74" s="1" t="s">
+      <c r="DO76" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="DP74" s="1" t="s">
+      <c r="DP76" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="DQ74" s="1" t="s">
+      <c r="DQ76" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="DR74" s="1" t="s">
+      <c r="DR76" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="DS74" s="1" t="s">
+      <c r="DS76" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="DT74" s="1" t="s">
+      <c r="DT76" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="DU74" s="1" t="s">
+      <c r="DU76" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="DV74" s="1" t="s">
+      <c r="DV76" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="DW74" s="1" t="s">
+      <c r="DW76" s="1" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="75" spans="1:127" x14ac:dyDescent="0.2">
-      <c r="A75" s="1">
+    <row r="77" spans="1:127" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
         <v>40856</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C77" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="D75" s="1">
+      <c r="D77" s="1">
         <v>3556837</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E77" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="F75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I75" s="1" t="s">
+      <c r="F77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I77" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="J75" s="1" t="s">
+      <c r="J77" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="K75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="L75" s="1" t="s">
+      <c r="K77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="L77" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="M75" s="1">
-        <v>0</v>
-      </c>
-      <c r="N75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="O75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="P75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="R75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="S75" s="1">
-        <v>0</v>
-      </c>
-      <c r="T75" s="1" t="s">
+      <c r="M77" s="1">
+        <v>0</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="P77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="R77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="S77" s="1">
+        <v>0</v>
+      </c>
+      <c r="T77" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="U75" s="1" t="s">
+      <c r="U77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="V75" s="1" t="s">
+      <c r="V77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="W75" s="1" t="s">
+      <c r="W77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="X75" s="1" t="s">
+      <c r="X77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="Y75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="Z75" s="1" t="s">
+      <c r="Y77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z77" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="1" t="s">
+      <c r="AA77" s="8"/>
+      <c r="AB77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AC75" s="1" t="s">
+      <c r="AC77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AD75" s="1" t="s">
+      <c r="AD77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AE75" s="1" t="s">
+      <c r="AE77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AF75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AG75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AH75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AI75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AJ75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AK75" s="1" t="s">
+      <c r="AF77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AG77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AH77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AI77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AJ77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AK77" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="AL75" s="1" t="s">
+      <c r="AL77" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="AM75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AN75" s="1" t="s">
+      <c r="AM77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AN77" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="AO75" s="1" t="s">
+      <c r="AO77" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="AP75" s="1">
+      <c r="AP77" s="1">
         <v>80299</v>
       </c>
-      <c r="AQ75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AR75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AS75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AT75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AU75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AV75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AW75" s="1" t="s">
+      <c r="AQ77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AR77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AS77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AT77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AU77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AV77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AW77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="AX75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AY75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="AZ75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BA75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BB75" s="1" t="s">
+      <c r="AX77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AY77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="AZ77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BA77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BB77" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="BC75" s="1" t="s">
+      <c r="BC77" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="BD75" s="1">
+      <c r="BD77" s="1">
         <v>80299</v>
       </c>
-      <c r="BE75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BF75" s="1">
+      <c r="BE77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BF77" s="1">
         <v>80326</v>
       </c>
-      <c r="BG75" s="1">
+      <c r="BG77" s="1">
         <v>80326</v>
       </c>
-      <c r="BH75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BI75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BJ75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BK75" s="1" t="s">
+      <c r="BH77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BI77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BJ77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BK77" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="BL75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BM75" s="1">
+      <c r="BL77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BM77" s="1">
         <v>2367611</v>
       </c>
-      <c r="BN75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BO75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BP75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BQ75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BR75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BS75" s="1" t="s">
+      <c r="BN77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BO77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BP77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BQ77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BR77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BS77" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="BT75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="BU75" s="1" t="s">
+      <c r="BT77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="BU77" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="BV75" s="1" t="s">
+      <c r="BV77" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="BW75" s="1" t="s">
+      <c r="BW77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="BX75" s="1" t="s">
+      <c r="BX77" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="BY75" s="1" t="s">
+      <c r="BY77" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="BZ75" s="1" t="s">
+      <c r="BZ77" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="CA75" s="1" t="s">
+      <c r="CA77" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="CB75" s="1" t="s">
+      <c r="CB77" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="CC75" s="1" t="s">
+      <c r="CC77" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="CD75" s="1" t="s">
+      <c r="CD77" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="CE75" s="1" t="s">
+      <c r="CE77" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="CF75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="CG75" s="7">
+      <c r="CF77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="CG77" s="7">
         <v>44138</v>
       </c>
-      <c r="CH75" s="7">
+      <c r="CH77" s="7">
         <v>44165</v>
       </c>
-      <c r="CI75" s="1" t="s">
+      <c r="CI77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="CJ75" s="1" t="s">
+      <c r="CJ77" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="CK75" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="CL75" s="1" t="s">
+      <c r="CK77" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="CL77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="CM75" s="1" t="s">
+      <c r="CM77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="CN75" s="1" t="s">
+      <c r="CN77" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="CO75" s="1" t="s">
+      <c r="CO77" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="CP75" s="1" t="s">
+      <c r="CP77" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="CQ75" s="1" t="s">
+      <c r="CQ77" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="CR75" s="1" t="s">
+      <c r="CR77" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="CS75" s="1" t="s">
+      <c r="CS77" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="CT75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="CU75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="CV75" s="1" t="s">
+      <c r="CT77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="CU77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="CV77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="CW75" s="1" t="s">
+      <c r="CW77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="CX75" s="1" t="s">
+      <c r="CX77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="CY75" s="1" t="s">
+      <c r="CY77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="CZ75" s="1" t="s">
+      <c r="CZ77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="DA75" s="1" t="s">
+      <c r="DA77" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="DB75" s="1" t="s">
+      <c r="DB77" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="DC75" s="1" t="s">
+      <c r="DC77" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="DD75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="DE75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="DF75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="DG75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="DH75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="DJ75" s="1" t="s">
+      <c r="DD77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DE77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DF77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DG77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DH77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DJ77" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="DK75" s="1">
-        <v>0</v>
-      </c>
-      <c r="DL75" s="1">
-        <v>0</v>
-      </c>
-      <c r="DM75" s="1">
-        <v>0</v>
-      </c>
-      <c r="DN75" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO75" s="1">
-        <v>0</v>
-      </c>
-      <c r="DP75" s="1">
-        <v>0</v>
-      </c>
-      <c r="DQ75" s="1" t="s">
+      <c r="DK77" s="1">
+        <v>0</v>
+      </c>
+      <c r="DL77" s="1">
+        <v>0</v>
+      </c>
+      <c r="DM77" s="1">
+        <v>0</v>
+      </c>
+      <c r="DN77" s="1">
+        <v>0</v>
+      </c>
+      <c r="DO77" s="1">
+        <v>0</v>
+      </c>
+      <c r="DP77" s="1">
+        <v>0</v>
+      </c>
+      <c r="DQ77" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="DR75" s="1" t="s">
+      <c r="DR77" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="DS75" s="1" t="s">
+      <c r="DS77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="DT75" s="1" t="s">
+      <c r="DT77" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="DU75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="DV75" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="DW75" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="78" spans="1:127" x14ac:dyDescent="0.2">
-      <c r="B78" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="C78" s="4" t="s">
+      <c r="DU77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DV77" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DW77" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="80" spans="1:127" x14ac:dyDescent="0.2">
+      <c r="B80" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D80" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E78" s="4" t="s">
+      <c r="E80" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="F80" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G78" s="4" t="s">
+      <c r="G80" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="H78" s="4" t="s">
+      <c r="H80" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="I78" s="4" t="s">
+      <c r="I80" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="J78" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="K78" s="4" t="s">
+      <c r="J80" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="K80" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="L78" s="4" t="s">
+      <c r="L80" s="4" t="s">
         <v>213</v>
-      </c>
-    </row>
-    <row r="79" spans="1:127" x14ac:dyDescent="0.2">
-      <c r="B79" s="4">
-        <v>1</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>397</v>
-      </c>
-      <c r="E79" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>399</v>
-      </c>
-      <c r="G79" s="4">
-        <v>1</v>
-      </c>
-      <c r="H79" s="4">
-        <v>1</v>
-      </c>
-      <c r="I79" s="4">
-        <v>1</v>
-      </c>
-      <c r="J79" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="K79" s="4">
-        <v>1</v>
-      </c>
-      <c r="L79" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="1:127" x14ac:dyDescent="0.2">
-      <c r="B80" s="4">
-        <v>2</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>400</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="E80" s="4" t="s">
-        <v>402</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="G80" s="4">
-        <v>1</v>
-      </c>
-      <c r="H80" s="4">
-        <v>1</v>
-      </c>
-      <c r="I80" s="4">
-        <v>1</v>
-      </c>
-      <c r="J80" s="4">
-        <v>0</v>
-      </c>
-      <c r="K80" s="4">
-        <v>1</v>
-      </c>
-      <c r="L80" s="4" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="81" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B81" s="4">
-        <v>112</v>
+        <v>1</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="G81" s="4">
         <v>1</v>
@@ -4192,59 +4178,59 @@
         <v>1</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B82" s="4">
-        <v>129</v>
+        <v>2</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="G82" s="4">
         <v>1</v>
       </c>
       <c r="H82" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I82" s="4">
         <v>1</v>
       </c>
-      <c r="J82" s="4" t="s">
-        <v>117</v>
+      <c r="J82" s="4">
+        <v>0</v>
       </c>
       <c r="K82" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B83" s="4">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>22</v>
+        <v>402</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>23</v>
+        <v>403</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>24</v>
+        <v>404</v>
       </c>
       <c r="G83" s="4">
         <v>1</v>
@@ -4255,31 +4241,31 @@
       <c r="I83" s="4">
         <v>1</v>
       </c>
-      <c r="J83" s="4">
-        <v>1</v>
+      <c r="J83" s="4" t="s">
+        <v>117</v>
       </c>
       <c r="K83" s="4">
         <v>1</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>0</v>
+        <v>405</v>
       </c>
     </row>
     <row r="84" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B84" s="4">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>25</v>
+        <v>406</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>26</v>
+        <v>407</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>27</v>
+        <v>408</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>28</v>
+        <v>409</v>
       </c>
       <c r="G84" s="4">
         <v>1</v>
@@ -4297,24 +4283,24 @@
         <v>0</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>0</v>
+        <v>405</v>
       </c>
     </row>
     <row r="85" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B85" s="4">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>413</v>
+        <v>21</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>414</v>
+        <v>22</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>415</v>
+        <v>23</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>416</v>
+        <v>24</v>
       </c>
       <c r="G85" s="4">
         <v>1</v>
@@ -4325,8 +4311,8 @@
       <c r="I85" s="4">
         <v>1</v>
       </c>
-      <c r="J85" s="4" t="s">
-        <v>117</v>
+      <c r="J85" s="4">
+        <v>1</v>
       </c>
       <c r="K85" s="4">
         <v>1</v>
@@ -4337,19 +4323,19 @@
     </row>
     <row r="86" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B86" s="4">
-        <v>197</v>
+        <v>173</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="D86" s="4">
-        <v>321654</v>
+        <v>25</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>418</v>
+        <v>27</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="G86" s="4">
         <v>1</v>
@@ -4372,25 +4358,25 @@
     </row>
     <row r="87" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B87" s="4">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="G87" s="4">
         <v>1</v>
       </c>
       <c r="H87" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I87" s="4">
         <v>1</v>
@@ -4399,7 +4385,7 @@
         <v>117</v>
       </c>
       <c r="K87" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="4" t="s">
         <v>0</v>
@@ -4407,19 +4393,19 @@
     </row>
     <row r="88" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B88" s="4">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="D88" s="4" t="s">
-        <v>424</v>
+        <v>414</v>
+      </c>
+      <c r="D88" s="4">
+        <v>321654</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>426</v>
+        <v>70</v>
       </c>
       <c r="G88" s="4">
         <v>1</v>
@@ -4442,25 +4428,25 @@
     </row>
     <row r="89" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B89" s="4">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="G89" s="4">
         <v>1</v>
       </c>
       <c r="H89" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I89" s="4">
         <v>1</v>
@@ -4469,7 +4455,7 @@
         <v>117</v>
       </c>
       <c r="K89" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="4" t="s">
         <v>0</v>
@@ -4477,19 +4463,19 @@
     </row>
     <row r="90" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B90" s="4">
-        <v>280</v>
+        <v>201</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="G90" s="4">
         <v>1</v>
@@ -4507,39 +4493,39 @@
         <v>0</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B91" s="4">
-        <v>292</v>
+        <v>203</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>67</v>
+        <v>424</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>68</v>
+        <v>425</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>69</v>
+        <v>426</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>70</v>
+        <v>427</v>
       </c>
       <c r="G91" s="4">
         <v>1</v>
       </c>
       <c r="H91" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>117</v>
       </c>
       <c r="K91" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="4" t="s">
         <v>0</v>
@@ -4547,19 +4533,19 @@
     </row>
     <row r="92" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B92" s="4">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="G92" s="4">
         <v>1</v>
@@ -4582,54 +4568,54 @@
     </row>
     <row r="93" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B93" s="4">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>436</v>
+        <v>67</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>436</v>
+        <v>68</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>437</v>
+        <v>69</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>438</v>
+        <v>70</v>
       </c>
       <c r="G93" s="4">
         <v>1</v>
       </c>
       <c r="H93" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I93" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" s="4" t="s">
         <v>117</v>
       </c>
       <c r="K93" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B94" s="4">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="G94" s="4">
         <v>1</v>
@@ -4647,30 +4633,30 @@
         <v>0</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>0</v>
+        <v>114</v>
       </c>
     </row>
     <row r="95" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B95" s="4">
-        <v>336</v>
+        <v>303</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>442</v>
+        <v>433</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>443</v>
+        <v>434</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="G95" s="4">
         <v>1</v>
       </c>
       <c r="H95" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" s="4">
         <v>1</v>
@@ -4679,112 +4665,182 @@
         <v>117</v>
       </c>
       <c r="K95" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>0</v>
+        <v>405</v>
       </c>
     </row>
     <row r="96" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B96" s="4">
+        <v>323</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="G96" s="4">
+        <v>1</v>
+      </c>
+      <c r="H96" s="4">
+        <v>0</v>
+      </c>
+      <c r="I96" s="4">
+        <v>1</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="K96" s="4">
+        <v>0</v>
+      </c>
+      <c r="L96" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B97" s="4">
+        <v>336</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="G97" s="4">
+        <v>1</v>
+      </c>
+      <c r="H97" s="4">
+        <v>0</v>
+      </c>
+      <c r="I97" s="4">
+        <v>1</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="K97" s="4">
+        <v>0</v>
+      </c>
+      <c r="L97" s="4" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B98" s="4">
         <v>337</v>
       </c>
-      <c r="C96" s="4" t="s">
+      <c r="C98" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="G98" s="4">
+        <v>1</v>
+      </c>
+      <c r="H98" s="4">
+        <v>1</v>
+      </c>
+      <c r="I98" s="4">
+        <v>0</v>
+      </c>
+      <c r="J98" s="4">
+        <v>0</v>
+      </c>
+      <c r="K98" s="4">
+        <v>0</v>
+      </c>
+      <c r="L98" s="4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="100" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D100" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="D96" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="E96" s="4" t="s">
+      <c r="E100" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="F96" s="4" t="s">
+      <c r="F100" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G100" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="G96" s="4">
-        <v>1</v>
-      </c>
-      <c r="H96" s="4">
-        <v>1</v>
-      </c>
-      <c r="I96" s="4">
-        <v>0</v>
-      </c>
-      <c r="J96" s="4">
-        <v>0</v>
-      </c>
-      <c r="K96" s="4">
-        <v>0</v>
-      </c>
-      <c r="L96" s="4" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="98" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D98" s="5" t="s">
+      <c r="H100" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="E98" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="F98" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="G98" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="H98" s="5" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="99" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D99" s="4" t="s">
+    </row>
+    <row r="101" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D101" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E99" s="4" t="s">
+      <c r="E101" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="F99" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G99" s="4">
+      <c r="F101" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="G101" s="4">
         <v>772</v>
       </c>
-      <c r="H99" s="18">
+      <c r="H101" s="18">
         <v>4784</v>
       </c>
     </row>
-    <row r="100" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D100" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="E100" s="4" t="s">
+    <row r="102" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D102" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F102" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="F100" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="G100" s="4">
+      <c r="G102" s="4">
         <v>1604</v>
       </c>
-      <c r="H100" s="18">
+      <c r="H102" s="18">
         <v>1838</v>
       </c>
     </row>
-    <row r="101" spans="4:8" x14ac:dyDescent="0.2">
-      <c r="D101" s="4" t="s">
-        <v>431</v>
-      </c>
-      <c r="E101" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="F101" s="4" t="s">
+    <row r="103" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="D103" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="F103" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="G101" s="4">
+      <c r="G103" s="4">
         <v>3</v>
       </c>
-      <c r="H101" s="18">
+      <c r="H103" s="18">
         <v>2475</v>
       </c>
     </row>
@@ -5250,52 +5306,52 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="O1" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E2" t="s">
+        <v>349</v>
+      </c>
+      <c r="G2" s="12" t="s">
         <v>350</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="G2" s="12" t="s">
+      <c r="I2" t="s">
         <v>352</v>
       </c>
-      <c r="H2" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="I2" t="s">
-        <v>354</v>
-      </c>
       <c r="O2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="O3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="G4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -5305,21 +5361,21 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="O5" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="G6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="H6" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="K6" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="O6" t="s">
         <v>311</v>
@@ -5327,64 +5383,64 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="O7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K8" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K9" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="O9" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K10" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="O10" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K11" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="O11" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K12" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="J14" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K15" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K16" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="17" spans="10:12" x14ac:dyDescent="0.3">
       <c r="K17" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="18" spans="10:12" x14ac:dyDescent="0.3">
@@ -5394,12 +5450,12 @@
     </row>
     <row r="19" spans="10:12" x14ac:dyDescent="0.3">
       <c r="K19" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="20" spans="10:12" x14ac:dyDescent="0.3">
       <c r="K20" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="22" spans="10:12" x14ac:dyDescent="0.3">
@@ -5410,18 +5466,18 @@
         <v>4</v>
       </c>
       <c r="L22" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="23" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J23" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="K23">
         <v>5</v>
       </c>
       <c r="L23" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="24" spans="10:12" x14ac:dyDescent="0.3">
@@ -5429,7 +5485,7 @@
         <v>6</v>
       </c>
       <c r="L24" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="25" spans="10:12" x14ac:dyDescent="0.3">
@@ -5437,7 +5493,7 @@
         <v>7</v>
       </c>
       <c r="L25" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="26" spans="10:12" x14ac:dyDescent="0.3">
@@ -5445,7 +5501,7 @@
         <v>8</v>
       </c>
       <c r="L26" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" spans="10:12" x14ac:dyDescent="0.3">
@@ -5453,12 +5509,12 @@
         <v>9</v>
       </c>
       <c r="L27" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="29" spans="10:12" x14ac:dyDescent="0.3">
       <c r="J29" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="30" spans="10:12" x14ac:dyDescent="0.3">
@@ -5468,7 +5524,7 @@
     </row>
     <row r="31" spans="10:12" x14ac:dyDescent="0.3">
       <c r="K31" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -5489,17 +5545,17 @@
     </row>
     <row r="3" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L3" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L6" s="20" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L7" s="12" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="12:13" x14ac:dyDescent="0.3">
@@ -5509,7 +5565,7 @@
     </row>
     <row r="9" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L9" s="12" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10" spans="12:13" x14ac:dyDescent="0.3">
@@ -5519,59 +5575,59 @@
     </row>
     <row r="11" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L11" s="12" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
     </row>
     <row r="12" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L12" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
     </row>
     <row r="13" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L13" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
     </row>
     <row r="14" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L14" s="12" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="15" spans="12:13" x14ac:dyDescent="0.3">
       <c r="L15" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="M15" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L17" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="M17" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L18" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="M18" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L19" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="M19" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L20" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="M20" t="s">
         <v>121</v>
@@ -5579,15 +5635,15 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L21" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="M21" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L22" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="M22" t="s">
         <v>262</v>
@@ -5595,7 +5651,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L23" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="M23" t="s">
         <v>262</v>
@@ -5603,81 +5659,81 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L24" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="M24" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L25" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M25" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L28" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="N28" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="L29" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="M29" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B30" s="20" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="L30" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="N30" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="L32" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
     </row>
     <row r="33" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
     </row>
     <row r="34" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="L34" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.3">
       <c r="L36" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.3">
@@ -5707,19 +5763,19 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B2" s="12" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="12"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B4" s="12" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
@@ -5731,17 +5787,17 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5762,18 +5818,18 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C13" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="D13" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="D14" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5794,30 +5850,30 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C17" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C18" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="21" spans="2:3" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
     </row>
   </sheetData>

--- a/Rowing.xlsx
+++ b/Rowing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Flutter\rowing_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F848B5-55C9-4145-ADB6-D709E768FFCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F904E58-F640-42CE-BFF5-B9D7AA94CA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{98999F70-D1D4-4A66-BAFC-041518B5B1BB}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="524">
   <si>
     <t>Rowing</t>
   </si>
@@ -1670,6 +1670,15 @@
   </si>
   <si>
     <t>SELECT IdUsuario, CODIGOGRUPO,CODIGOCAUSANTE,Login, Contrasena, Nombre, Apellido, HabilitaAPP, HabilitaFotos, HabilitaSSHH, HabilitaRRHH,HabilitaMedidores, HabilitaReclamos, HabilitaFlotas, Modulo</t>
+  </si>
+  <si>
+    <t>SELECT NroCausante, grupo, codigo,NroSAP, nombre, estado</t>
+  </si>
+  <si>
+    <t>FROM     Causantes</t>
+  </si>
+  <si>
+    <t>WHERE grupo='PPR' AND ESTADO='True'</t>
   </si>
 </sst>
 </file>
@@ -2518,6 +2527,9 @@
       </c>
     </row>
     <row r="17" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="F17" s="8" t="s">
+        <v>521</v>
+      </c>
       <c r="J17" s="1" t="s">
         <v>330</v>
       </c>
@@ -2526,6 +2538,9 @@
       </c>
     </row>
     <row r="18" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="F18" s="8" t="s">
+        <v>522</v>
+      </c>
       <c r="K18" s="3" t="s">
         <v>331</v>
       </c>
@@ -2542,6 +2557,9 @@
       </c>
       <c r="E19" s="5" t="s">
         <v>20</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>523</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>332</v>
